--- a/artfynd/A 36938-2023 artfynd.xlsx
+++ b/artfynd/A 36938-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119710735</v>
+        <v>119710793</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>90573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559151</v>
+        <v>559328</v>
       </c>
       <c r="R2" t="n">
-        <v>6433928</v>
+        <v>6433905</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119710755</v>
+        <v>119711312</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>90776</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,29 +793,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -824,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559151</v>
+        <v>559127</v>
       </c>
       <c r="R3" t="n">
-        <v>6433928</v>
+        <v>6434194</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119711312</v>
+        <v>119710755</v>
       </c>
       <c r="B4" t="n">
-        <v>90776</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,37 +907,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559127</v>
+        <v>559151</v>
       </c>
       <c r="R4" t="n">
-        <v>6434194</v>
+        <v>6433928</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119710793</v>
+        <v>119710735</v>
       </c>
       <c r="B5" t="n">
-        <v>90573</v>
+        <v>91884</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559328</v>
+        <v>559151</v>
       </c>
       <c r="R5" t="n">
-        <v>6433905</v>
+        <v>6433928</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 36938-2023 artfynd.xlsx
+++ b/artfynd/A 36938-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119710793</v>
+        <v>119711312</v>
       </c>
       <c r="B2" t="n">
-        <v>90573</v>
+        <v>90776</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559328</v>
+        <v>559127</v>
       </c>
       <c r="R2" t="n">
-        <v>6433905</v>
+        <v>6434194</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119711312</v>
+        <v>119710755</v>
       </c>
       <c r="B3" t="n">
-        <v>90776</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +801,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1101</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559127</v>
+        <v>559151</v>
       </c>
       <c r="R3" t="n">
-        <v>6434194</v>
+        <v>6433928</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119710755</v>
+        <v>119710793</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>90573</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559151</v>
+        <v>559328</v>
       </c>
       <c r="R4" t="n">
-        <v>6433928</v>
+        <v>6433905</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>

--- a/artfynd/A 36938-2023 artfynd.xlsx
+++ b/artfynd/A 36938-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119711312</v>
+        <v>119710793</v>
       </c>
       <c r="B2" t="n">
-        <v>90776</v>
+        <v>90573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1101</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559127</v>
+        <v>559328</v>
       </c>
       <c r="R2" t="n">
-        <v>6434194</v>
+        <v>6433905</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119710755</v>
+        <v>119710735</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119710793</v>
+        <v>119711312</v>
       </c>
       <c r="B4" t="n">
-        <v>90573</v>
+        <v>90776</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,29 +899,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>1101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559328</v>
+        <v>559127</v>
       </c>
       <c r="R4" t="n">
-        <v>6433905</v>
+        <v>6434194</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119710735</v>
+        <v>119710755</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 36938-2023 artfynd.xlsx
+++ b/artfynd/A 36938-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119710793</v>
+        <v>119711312</v>
       </c>
       <c r="B2" t="n">
-        <v>90573</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559328</v>
+        <v>559127</v>
       </c>
       <c r="R2" t="n">
-        <v>6433905</v>
+        <v>6434194</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,37 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119710735</v>
+        <v>119710793</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559151</v>
+        <v>559328</v>
       </c>
       <c r="R3" t="n">
-        <v>6433928</v>
+        <v>6433905</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119711312</v>
+        <v>119710755</v>
       </c>
       <c r="B4" t="n">
-        <v>90776</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,33 +896,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -938,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559127</v>
+        <v>559151</v>
       </c>
       <c r="R4" t="n">
-        <v>6434194</v>
+        <v>6433928</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,112 +983,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>119710755</v>
-      </c>
-      <c r="B5" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>NO Lillgryt, Ög</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>559151</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6433928</v>
-      </c>
-      <c r="S5" t="n">
-        <v>50</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Kinda</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Oppeby</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Magnus Wadstein</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Magnus Wadstein</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36938-2023 artfynd.xlsx
+++ b/artfynd/A 36938-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711312</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710793</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,8 +998,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119710755</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>